--- a/diseases/d088/2020-2025.xlsx
+++ b/diseases/d088/2020-2025.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
@@ -785,7 +790,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -796,6 +806,11 @@
       <c r="AT2" t="n">
         <v>1</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>is_doh_annual</t>
@@ -818,22 +833,22 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -860,17 +875,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -911,7 +926,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Bandormslirfusýki</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -919,6 +959,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -926,55 +1024,65 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1114,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1147,12 +1255,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1288,12 +1396,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1429,12 +1537,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1570,12 +1678,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1711,12 +1819,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1852,12 +1960,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1993,12 +2101,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2134,12 +2242,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2275,12 +2383,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2416,12 +2524,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2557,12 +2665,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2698,12 +2806,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2839,12 +2947,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2980,12 +3088,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3121,12 +3229,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3262,12 +3370,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3403,12 +3511,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-WKO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Waikato, New Zealand</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3544,12 +3652,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>NZ-WMT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Waitemata, New Zealand</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3574,12 +3682,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2021-01</t>
+          <t>2020-01</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3588,12 +3696,9 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3613,7 +3718,7 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
         </is>
       </c>
       <c r="AT22" t="n">
@@ -3621,42 +3726,42 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd; ecdc_atlas_annual</t>
+          <t>phf_dhb_annual</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly; ECDC Surveillance Atlas — Iceland Annual Baseline</t>
+          <t>New Zealand PHF Science Annual DHB Data</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel; official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3793,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3732,9 +3837,17 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3749,55 +3862,65 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT23" t="n">
         <v>1</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3824,17 +3947,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3875,7 +3998,32 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Bandormslirfusýki</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3883,6 +4031,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN24" t="b">
+        <v>1</v>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -3890,55 +4096,65 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+          <t>SER_IS_HISTORY_CYSTICERCOSIS_ANNUAL</t>
         </is>
       </c>
       <c r="AT24" t="n">
         <v>1</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>phf_dhb_annual</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Annual DHB Data</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3970,12 +4186,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4111,12 +4327,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4252,12 +4468,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4393,12 +4609,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4534,12 +4750,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4675,12 +4891,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4816,12 +5032,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4957,12 +5173,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5098,12 +5314,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5239,12 +5455,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5380,12 +5596,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5521,12 +5737,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5662,12 +5878,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5803,12 +6019,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5944,12 +6160,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6085,12 +6301,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6226,12 +6442,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -6367,12 +6583,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>NZ-WKO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Waikato, New Zealand</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -6397,12 +6613,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6508,12 +6724,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>NZ-WMT</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Waitemata, New Zealand</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6538,12 +6754,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2022-01</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6649,12 +6865,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6790,12 +7006,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6931,12 +7147,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7072,12 +7288,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7213,12 +7429,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -7354,12 +7570,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -7495,12 +7711,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7636,12 +7852,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7777,12 +7993,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7918,12 +8134,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8059,12 +8275,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8200,12 +8416,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8341,12 +8557,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8482,12 +8698,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8623,12 +8839,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -8764,12 +8980,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8905,12 +9121,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9046,12 +9262,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>NZ-WKO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Waikato, New Zealand</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9076,12 +9292,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -9187,12 +9403,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>NZ-WMT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Waitemata, New Zealand</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9217,12 +9433,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2023-01</t>
+          <t>2022-01</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -9328,12 +9544,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -9469,12 +9685,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -9610,12 +9826,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9751,12 +9967,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -9892,12 +10108,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10033,12 +10249,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10174,12 +10390,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10315,12 +10531,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10456,12 +10672,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -10597,12 +10813,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -10738,12 +10954,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10879,12 +11095,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11020,12 +11236,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11161,12 +11377,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11302,12 +11518,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -11443,12 +11659,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -11584,12 +11800,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -11725,12 +11941,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>NZ-WKO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Waikato, New Zealand</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -11755,12 +11971,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -11866,12 +12082,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>NZ-WMT</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Waitemata, New Zealand</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -11896,12 +12112,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -12007,12 +12223,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12148,12 +12364,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -12289,12 +12505,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -12430,12 +12646,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -12571,12 +12787,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -12712,12 +12928,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -12853,12 +13069,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -12994,12 +13210,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -13135,12 +13351,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -13276,12 +13492,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -13417,12 +13633,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -13558,12 +13774,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -13699,12 +13915,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -13840,12 +14056,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -13981,12 +14197,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -14122,12 +14338,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -14263,12 +14479,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -14404,12 +14620,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NZ-AKL</t>
+          <t>NZ-WKO</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Waikato, New Zealand</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -14434,12 +14650,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -14545,12 +14761,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NZ-BOP</t>
+          <t>NZ-WMT</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bay of Plenty, New Zealand</t>
+          <t>Waitemata, New Zealand</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -14575,12 +14791,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="N100" t="n">
@@ -14686,12 +14902,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NZ-CAN</t>
+          <t>NZ-AKL</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Canterbury, New Zealand</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -14827,12 +15043,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NZ-CCH</t>
+          <t>NZ-BOP</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Capital, Coast and Hutt Valley, New Zealand</t>
+          <t>Bay of Plenty, New Zealand</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -14968,12 +15184,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>NZ-CMN</t>
+          <t>NZ-CAN</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Counties Manukau, New Zealand</t>
+          <t>Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -15109,12 +15325,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>NZ-HKB</t>
+          <t>NZ-CCH</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hawke's Bay, New Zealand</t>
+          <t>Capital, Coast and Hutt Valley, New Zealand</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -15250,12 +15466,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>NZ-LKS</t>
+          <t>NZ-CMN</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lakes, New Zealand</t>
+          <t>Counties Manukau, New Zealand</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -15391,12 +15607,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>NZ-MDC</t>
+          <t>NZ-HKB</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>MidCentral, New Zealand</t>
+          <t>Hawke's Bay, New Zealand</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -15532,12 +15748,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NZ-NMB</t>
+          <t>NZ-LKS</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nelson Marlborough, New Zealand</t>
+          <t>Lakes, New Zealand</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -15673,12 +15889,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>NZ-NTH</t>
+          <t>NZ-MDC</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Northland, New Zealand</t>
+          <t>MidCentral, New Zealand</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -15814,12 +16030,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>NZ-SCT</t>
+          <t>NZ-NMB</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>South Canterbury, New Zealand</t>
+          <t>Nelson Marlborough, New Zealand</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -15955,12 +16171,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>NZ-SOU</t>
+          <t>NZ-NTH</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Southern, New Zealand</t>
+          <t>Northland, New Zealand</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -16096,12 +16312,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>NZ-TAI</t>
+          <t>NZ-SCT</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tairawhiti, New Zealand</t>
+          <t>South Canterbury, New Zealand</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -16237,12 +16453,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>NZ-TAR</t>
+          <t>NZ-SOU</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Taranaki, New Zealand</t>
+          <t>Southern, New Zealand</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -16378,12 +16594,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>NZ-WAI</t>
+          <t>NZ-TAI</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Wairarapa, New Zealand</t>
+          <t>Tairawhiti, New Zealand</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -16519,12 +16735,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>NZ-WCT</t>
+          <t>NZ-TAR</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>West Coast, New Zealand</t>
+          <t>Taranaki, New Zealand</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -16660,12 +16876,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>NZ-WHG</t>
+          <t>NZ-WAI</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Whanganui, New Zealand</t>
+          <t>Wairarapa, New Zealand</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -16801,12 +17017,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>NZ-WKO</t>
+          <t>NZ-WCT</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Waikato, New Zealand</t>
+          <t>West Coast, New Zealand</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -16942,12 +17158,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>NZ-WMT</t>
+          <t>NZ-WHG</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Waitemata, New Zealand</t>
+          <t>Whanganui, New Zealand</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -17050,6 +17266,288 @@
         </is>
       </c>
       <c r="BC117" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>cysticercosis</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>NZ-WKO</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Waikato, New Zealand</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>囊虫病</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>cysticercosis</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>NZ-WMT</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Waitemata, New Zealand</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D088</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Cysticercosis</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>囊虫病</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>HOLD_NZ_b4173e42542bf2ee920eef1fc6bc</t>
+        </is>
+      </c>
+      <c r="AT119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>phf_dhb_annual</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Annual DHB Data</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/ESR-NZ/Notifiable-Diseases-Annual-Dashboard-/main/data/DHB_Total.csv</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -17181,7 +17679,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
@@ -17201,7 +17699,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -17211,7 +17709,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
